--- a/figures/lecture5/6345.0/634507a.xlsx
+++ b/figures/lecture5/6345.0/634507a.xlsx
@@ -17,44 +17,44 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A2707474F">Data1!$E$1:$E$10,Data1!$E$11:$E$36</definedName>
-    <definedName name="A2707474F_Data">Data1!$E$11:$E$36</definedName>
-    <definedName name="A2707474F_Latest">Data1!$E$36</definedName>
-    <definedName name="A2707588C">Data1!$G$1:$G$10,Data1!$G$11:$G$36</definedName>
-    <definedName name="A2707588C_Data">Data1!$G$11:$G$36</definedName>
-    <definedName name="A2707588C_Latest">Data1!$G$36</definedName>
-    <definedName name="A2707664V">Data1!$F$1:$F$10,Data1!$F$11:$F$36</definedName>
-    <definedName name="A2707664V_Data">Data1!$F$11:$F$36</definedName>
-    <definedName name="A2707664V_Latest">Data1!$F$36</definedName>
-    <definedName name="A2709868J">Data1!$B$1:$B$10,Data1!$B$11:$B$36</definedName>
-    <definedName name="A2709868J_Data">Data1!$B$11:$B$36</definedName>
-    <definedName name="A2709868J_Latest">Data1!$B$36</definedName>
-    <definedName name="A2709982L">Data1!$D$1:$D$10,Data1!$D$11:$D$36</definedName>
-    <definedName name="A2709982L_Data">Data1!$D$11:$D$36</definedName>
-    <definedName name="A2709982L_Latest">Data1!$D$36</definedName>
-    <definedName name="A2710058C">Data1!$C$1:$C$10,Data1!$C$11:$C$36</definedName>
-    <definedName name="A2710058C_Data">Data1!$C$11:$C$36</definedName>
-    <definedName name="A2710058C_Latest">Data1!$C$36</definedName>
-    <definedName name="A85019935L">Data1!$H$1:$H$10,Data1!$H$11:$H$36</definedName>
-    <definedName name="A85019935L_Data">Data1!$H$11:$H$36</definedName>
-    <definedName name="A85019935L_Latest">Data1!$H$36</definedName>
-    <definedName name="A85020011K">Data1!$K$1:$K$10,Data1!$K$11:$K$36</definedName>
-    <definedName name="A85020011K_Data">Data1!$K$11:$K$36</definedName>
-    <definedName name="A85020011K_Latest">Data1!$K$36</definedName>
-    <definedName name="A85020061J">Data1!$I$1:$I$10,Data1!$I$11:$I$36</definedName>
-    <definedName name="A85020061J_Data">Data1!$I$11:$I$36</definedName>
-    <definedName name="A85020061J_Latest">Data1!$I$36</definedName>
-    <definedName name="A85020601K">Data1!$L$1:$L$10,Data1!$L$11:$L$36</definedName>
-    <definedName name="A85020601K_Data">Data1!$L$11:$L$36</definedName>
-    <definedName name="A85020601K_Latest">Data1!$L$36</definedName>
-    <definedName name="A85020667A">Data1!$J$1:$J$10,Data1!$J$11:$J$36</definedName>
-    <definedName name="A85020667A_Data">Data1!$J$11:$J$36</definedName>
-    <definedName name="A85020667A_Latest">Data1!$J$36</definedName>
-    <definedName name="A85020743T">Data1!$M$1:$M$10,Data1!$M$11:$M$36</definedName>
-    <definedName name="A85020743T_Data">Data1!$M$11:$M$36</definedName>
-    <definedName name="A85020743T_Latest">Data1!$M$36</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$36</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$36</definedName>
+    <definedName name="A2707474F">Data1!$E$1:$E$10,Data1!$E$11:$E$38</definedName>
+    <definedName name="A2707474F_Data">Data1!$E$11:$E$38</definedName>
+    <definedName name="A2707474F_Latest">Data1!$E$38</definedName>
+    <definedName name="A2707588C">Data1!$G$1:$G$10,Data1!$G$11:$G$38</definedName>
+    <definedName name="A2707588C_Data">Data1!$G$11:$G$38</definedName>
+    <definedName name="A2707588C_Latest">Data1!$G$38</definedName>
+    <definedName name="A2707664V">Data1!$F$1:$F$10,Data1!$F$11:$F$38</definedName>
+    <definedName name="A2707664V_Data">Data1!$F$11:$F$38</definedName>
+    <definedName name="A2707664V_Latest">Data1!$F$38</definedName>
+    <definedName name="A2709868J">Data1!$B$1:$B$10,Data1!$B$11:$B$38</definedName>
+    <definedName name="A2709868J_Data">Data1!$B$11:$B$38</definedName>
+    <definedName name="A2709868J_Latest">Data1!$B$38</definedName>
+    <definedName name="A2709982L">Data1!$D$1:$D$10,Data1!$D$11:$D$38</definedName>
+    <definedName name="A2709982L_Data">Data1!$D$11:$D$38</definedName>
+    <definedName name="A2709982L_Latest">Data1!$D$38</definedName>
+    <definedName name="A2710058C">Data1!$C$1:$C$10,Data1!$C$11:$C$38</definedName>
+    <definedName name="A2710058C_Data">Data1!$C$11:$C$38</definedName>
+    <definedName name="A2710058C_Latest">Data1!$C$38</definedName>
+    <definedName name="A85019935L">Data1!$H$1:$H$10,Data1!$H$11:$H$38</definedName>
+    <definedName name="A85019935L_Data">Data1!$H$11:$H$38</definedName>
+    <definedName name="A85019935L_Latest">Data1!$H$38</definedName>
+    <definedName name="A85020011K">Data1!$K$1:$K$10,Data1!$K$11:$K$38</definedName>
+    <definedName name="A85020011K_Data">Data1!$K$11:$K$38</definedName>
+    <definedName name="A85020011K_Latest">Data1!$K$38</definedName>
+    <definedName name="A85020061J">Data1!$I$1:$I$10,Data1!$I$11:$I$38</definedName>
+    <definedName name="A85020061J_Data">Data1!$I$11:$I$38</definedName>
+    <definedName name="A85020061J_Latest">Data1!$I$38</definedName>
+    <definedName name="A85020601K">Data1!$L$1:$L$10,Data1!$L$11:$L$38</definedName>
+    <definedName name="A85020601K_Data">Data1!$L$11:$L$38</definedName>
+    <definedName name="A85020601K_Latest">Data1!$L$38</definedName>
+    <definedName name="A85020667A">Data1!$J$1:$J$10,Data1!$J$11:$J$38</definedName>
+    <definedName name="A85020667A_Data">Data1!$J$11:$J$38</definedName>
+    <definedName name="A85020667A_Latest">Data1!$J$38</definedName>
+    <definedName name="A85020743T">Data1!$M$1:$M$10,Data1!$M$11:$M$38</definedName>
+    <definedName name="A85020743T_Data">Data1!$M$11:$M$38</definedName>
+    <definedName name="A85020743T_Latest">Data1!$M$38</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$38</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$38</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -662,7 +662,7 @@
     <t>Freq.</t>
   </si>
   <si>
-    <t>© Commonwealth of Australia  2023</t>
+    <t>© Commonwealth of Australia  2026</t>
   </si>
 </sst>
 </file>
@@ -1343,10 +1343,10 @@
         <v>35947</v>
       </c>
       <c r="G12" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H12" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>21</v>
@@ -1375,10 +1375,10 @@
         <v>35947</v>
       </c>
       <c r="G13" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H13" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>21</v>
@@ -1407,10 +1407,10 @@
         <v>35947</v>
       </c>
       <c r="G14" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H14" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>21</v>
@@ -1439,10 +1439,10 @@
         <v>35947</v>
       </c>
       <c r="G15" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H15" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>21</v>
@@ -1471,10 +1471,10 @@
         <v>35947</v>
       </c>
       <c r="G16" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H16" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>21</v>
@@ -1503,10 +1503,10 @@
         <v>35947</v>
       </c>
       <c r="G17" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H17" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>21</v>
@@ -1535,10 +1535,10 @@
         <v>35947</v>
       </c>
       <c r="G18" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H18" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>31</v>
@@ -1567,10 +1567,10 @@
         <v>35947</v>
       </c>
       <c r="G19" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H19" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>31</v>
@@ -1599,10 +1599,10 @@
         <v>35947</v>
       </c>
       <c r="G20" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H20" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>31</v>
@@ -1631,10 +1631,10 @@
         <v>35947</v>
       </c>
       <c r="G21" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H21" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>31</v>
@@ -1663,10 +1663,10 @@
         <v>35947</v>
       </c>
       <c r="G22" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H22" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>31</v>
@@ -1695,10 +1695,10 @@
         <v>35947</v>
       </c>
       <c r="G23" s="9">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H23" s="10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>31</v>
@@ -1745,7 +1745,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -2040,40 +2040,40 @@
         <v>18</v>
       </c>
       <c r="B8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="C8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="D8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="E8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="F8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="G8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="H8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="I8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="J8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="K8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="L8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
       <c r="M8" s="6">
-        <v>45078</v>
+        <v>45809</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -2081,40 +2081,40 @@
         <v>19</v>
       </c>
       <c r="B9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M9" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
@@ -3210,6 +3210,88 @@
       </c>
       <c r="M36" s="8">
         <v>3.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>45444</v>
+      </c>
+      <c r="B37" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="C37" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="D37" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="E37" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="F37" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="G37" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="H37" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="I37" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="J37" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="K37" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="L37" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="M37" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>45809</v>
+      </c>
+      <c r="B38" s="8">
+        <v>156.69999999999999</v>
+      </c>
+      <c r="C38" s="8">
+        <v>156.4</v>
+      </c>
+      <c r="D38" s="8">
+        <v>156.69999999999999</v>
+      </c>
+      <c r="E38" s="8">
+        <v>156.6</v>
+      </c>
+      <c r="F38" s="8">
+        <v>156.5</v>
+      </c>
+      <c r="G38" s="8">
+        <v>156.69999999999999</v>
+      </c>
+      <c r="H38" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="I38" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="J38" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="K38" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="L38" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="M38" s="8">
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>
